--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>10</t>
+    <t>13</t>
   </si>
   <si>
     <t>Level</t>
@@ -202,6 +202,24 @@
   </si>
   <si>
     <t>Tiers de confiance</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>Document de Circulation pour étranger mineur</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>Acte de naissance + Carte vitale avec photo</t>
+  </si>
+  <si>
+    <t>IE</t>
+  </si>
+  <si>
+    <t>Identification électronique EIDAS</t>
   </si>
 </sst>
 </file>
@@ -519,7 +537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -546,7 +564,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -558,7 +578,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -570,7 +592,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -582,7 +606,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -594,7 +620,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -606,7 +634,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -618,7 +648,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -630,7 +662,9 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -642,7 +676,9 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -654,7 +690,51 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>13</t>
+    <t>10</t>
   </si>
   <si>
     <t>Level</t>
@@ -202,24 +202,6 @@
   </si>
   <si>
     <t>Tiers de confiance</t>
-  </si>
-  <si>
-    <t>DC</t>
-  </si>
-  <si>
-    <t>Document de Circulation pour étranger mineur</t>
-  </si>
-  <si>
-    <t>AC</t>
-  </si>
-  <si>
-    <t>Acte de naissance + Carte vitale avec photo</t>
-  </si>
-  <si>
-    <t>IE</t>
-  </si>
-  <si>
-    <t>Identification électronique EIDAS</t>
   </si>
 </sst>
 </file>
@@ -537,7 +519,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -564,9 +546,7 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" t="s" s="2">
-        <v>44</v>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -578,9 +558,7 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" t="s" s="2">
-        <v>46</v>
-      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -592,9 +570,7 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" t="s" s="2">
-        <v>48</v>
-      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -606,9 +582,7 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" t="s" s="2">
-        <v>50</v>
-      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -620,9 +594,7 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" t="s" s="2">
-        <v>52</v>
-      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -634,9 +606,7 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>54</v>
-      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -648,9 +618,7 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>56</v>
-      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -662,9 +630,7 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" t="s" s="2">
-        <v>58</v>
-      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -676,9 +642,7 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" t="s" s="2">
-        <v>60</v>
-      </c>
+      <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -690,51 +654,7 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" t="s" s="2">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>68</v>
-      </c>
+      <c r="D11" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>10</t>
+    <t>13</t>
   </si>
   <si>
     <t>Level</t>
@@ -202,6 +202,24 @@
   </si>
   <si>
     <t>Tiers de confiance</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>Document de Circulation pour étranger mineur</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>Acte de naissance + Carte vitale avec photo</t>
+  </si>
+  <si>
+    <t>IE</t>
+  </si>
+  <si>
+    <t>Identification électronique EIDAS</t>
   </si>
 </sst>
 </file>
@@ -519,7 +537,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -546,7 +564,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -558,7 +578,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -570,7 +592,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -582,7 +606,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -594,7 +620,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -606,7 +634,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -618,7 +648,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -630,7 +662,9 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -642,7 +676,9 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -654,7 +690,51 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
